--- a/data/trans_dic/P55$amigo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,62</t>
+          <t>0,0; 26,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 18,42</t>
+          <t>3,39; 16,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 14,93</t>
+          <t>2,47; 13,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 8,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,14</t>
+          <t>4,42; 14,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,12</t>
+          <t>1,59; 10,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 11,6</t>
+          <t>0,88; 11,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 12,84</t>
+          <t>5,08; 12,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,7</t>
+          <t>0,99; 6,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,6</t>
+          <t>0,66; 7,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,91</t>
+          <t>2,75; 6,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,85</t>
+          <t>0,34; 2,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,59</t>
+          <t>0,47; 4,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,71</t>
+          <t>2,55; 5,75</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,71; 9,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,22</t>
+          <t>2,39; 7,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,35; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,82</t>
+          <t>0,92; 5,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,34</t>
+          <t>3,7; 7,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,91; 3,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,91</t>
+          <t>0,72; 3,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,06</t>
+          <t>0,92; 4,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,81</t>
+          <t>3,53; 6,74</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11218</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>0; 3960</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 11190</t>
+          <t>0; 12112</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1378,47 +1378,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2061; 9285</t>
+          <t>1866; 9151</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1827; 10104</t>
+          <t>1669; 9344</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 6257</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8049</t>
+          <t>0; 7276</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3306; 10327</t>
+          <t>3560; 11292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1877; 11074</t>
+          <t>1746; 11290</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1013; 13356</t>
+          <t>1017; 13686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 8239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6553; 15848</t>
+          <t>6890; 16696</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>15222</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5612</t>
+          <t>0; 6923</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5662</t>
+          <t>0; 5414</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5098</t>
+          <t>0; 4398</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1240; 7145</t>
+          <t>1133; 7045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6830</t>
+          <t>0; 5871</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7286</t>
+          <t>0; 6659</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1226; 12231</t>
+          <t>1225; 13302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6915; 17647</t>
+          <t>7622; 19163</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8439</t>
+          <t>0; 7786</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1058; 8854</t>
+          <t>1057; 8711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2194; 12650</t>
+          <t>1299; 12708</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9380; 20680</t>
+          <t>9953; 22486</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>26440</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6390</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1039; 14098</t>
+          <t>1040; 13502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3890; 12919</t>
+          <t>4040; 12583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2066; 11894</t>
+          <t>2095; 11614</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>994; 8357</t>
+          <t>985; 8554</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2478; 15565</t>
+          <t>2472; 14437</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11911; 24099</t>
+          <t>13233; 26954</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3573; 13827</t>
+          <t>3256; 14253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3156; 16662</t>
+          <t>3047; 16801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3260; 15803</t>
+          <t>3582; 16601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18037; 33050</t>
+          <t>18597; 35462</t>
         </is>
       </c>
     </row>
